--- a/ONCHO/Entomological survey Survey/Nigeria/2025/enugu-kaduna/sites.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2025/enugu-kaduna/sites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\enugu-kaduna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\enugu-kaduna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D537B69A-CA0D-475E-BCF8-BD3D2276C161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D56FF8-3077-41CD-B73C-E71E3EA46DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BE50F1A-DFCC-4B63-9F45-FF2F2A6DD4D6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7BE50F1A-DFCC-4B63-9F45-FF2F2A6DD4D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="211">
   <si>
     <t>LGA</t>
   </si>
@@ -663,6 +663,12 @@
   </si>
   <si>
     <t>O. EJI NDIAGU AKPUGO</t>
+  </si>
+  <si>
+    <t>ENU_ENE_M_096</t>
+  </si>
+  <si>
+    <t>UGWOGO</t>
   </si>
 </sst>
 </file>
@@ -821,7 +827,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -870,12 +876,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{3938B651-D46A-48BA-A2D8-05D5BC138828}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1196,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD83EFE8-B67B-49E6-A276-5C214FFAD255}">
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
@@ -3861,7 +3888,10 @@
         <v>202</v>
       </c>
     </row>
-    <row r="97" spans="2:14">
+    <row r="97" spans="1:14">
+      <c r="A97" s="12">
+        <v>96</v>
+      </c>
       <c r="B97" s="19" t="s">
         <v>103</v>
       </c>
@@ -3881,23 +3911,36 @@
       <c r="M97" s="21"/>
       <c r="N97" s="21"/>
     </row>
-    <row r="98" spans="2:14">
-      <c r="J98"/>
-      <c r="K98"/>
-      <c r="M98"/>
-      <c r="N98"/>
-    </row>
-    <row r="99" spans="2:14">
-      <c r="M99"/>
-      <c r="N99"/>
+    <row r="98" spans="1:14">
+      <c r="A98" s="28">
+        <v>96</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C98" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D98" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E98" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M2:N99">
-    <sortCondition ref="M2:M99"/>
-    <sortCondition ref="N2:N99"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M2:N97">
+    <sortCondition ref="M2:M97"/>
+    <sortCondition ref="N2:N97"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="N2:N96">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
